--- a/Tareas en grupo/Metricas Cvat.xlsx
+++ b/Tareas en grupo/Metricas Cvat.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ciencias\CalidadSofwtareBSPO\Tareas en grupo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ciencias\Calidad de software - BSPOO\Tareas en grupo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D2AA214D-BCDE-40EC-BA85-02E11EE75329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35FE015E-5EF3-4F94-9409-9CBED4E428EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{5CAAA99B-0B29-425F-89B8-4D79C8DE75EE}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{5CAAA99B-0B29-425F-89B8-4D79C8DE75EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="229">
   <si>
     <t>Subcaracteristica</t>
   </si>
@@ -170,23 +170,6 @@
     <t>X = Nº líneas testadas / Nº líneas totales</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">X = Nº funciones con try-catch / Nº funciones
-críticas
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Funciones con recuperación de fallos</t>
-    </r>
-  </si>
-  <si>
     <t>X = Nº mecanismos (fallback, reintentos) / Nº casos críticos</t>
   </si>
   <si>
@@ -478,6 +461,489 @@
   <si>
     <t>X = Nº temas de ayuda cubiertos / Nº módulos
 principales</t>
+  </si>
+  <si>
+    <t>Descripción</t>
+  </si>
+  <si>
+    <t>Mide qué tan independientes y bien definidos están los módulos. Una alta cohesión implica que cada módulo tiene una responsabilidad clara.</t>
+  </si>
+  <si>
+    <t>Detalle</t>
+  </si>
+  <si>
+    <t>Mide qué tan desacoplados están los módulos. Un módulo "independiente" es aquel que no depende excesivamente de otros para funcionar.</t>
+  </si>
+  <si>
+    <t>Evalúa qué tan limpias y simples son las interfaces entre componentes (APIs, contratos entre capas).</t>
+  </si>
+  <si>
+    <t>Indica cuántos componentes han sido diseñados para ser reutilizados (ya sea dentro del proyecto o entre proyectos).</t>
+  </si>
+  <si>
+    <t>X=1 significa sin duplicación.
+Un valor bajo indica que cambios deben replicarse en múltiples lugares, aumentando el riesgo de errores. En CVAT, duplicar lógica de anotación en frontend y backend sería una mala práctica.</t>
+  </si>
+  <si>
+    <t>Cuenta los caminos linealmente independientes en una función (if, loops, case).
+Valores bajos (≤ 10) → función fácil de probar y comprender.
+En CVAT, funciones con alta complejidad ciclomática (ej. procesamiento de formatos de anotación con muchos casos especiales) son candidatas a refactorización.</t>
+  </si>
+  <si>
+    <t>Mide la densidad de documentación en el código fuente.
+Un valor muy bajo puede indicar código poco documentado.
+Un valor muy alto puede indicar comentarios redundantes o código confuso que requiere excesiva explicación.
+Lo ideal es que los comentarios expliquen el porqué no el qué.</t>
+  </si>
+  <si>
+    <t>Niveles de puntuación</t>
+  </si>
+  <si>
+    <t>Criterios de evaluacion</t>
+  </si>
+  <si>
+    <t>* Alto (0.8 – 1.0): Módulos bien definidos e independientes
+* Medio (0.5 – 0.79): Dependencias moderadas
+* Bajo (0 – 0.49): Alta dependencia entre módulos</t>
+  </si>
+  <si>
+    <t>* Existencia de separación clara de responsabilidades
+* Bajo acoplamiento entre módulos
+* Uso de arquitectura (ej: microservicios o capas)</t>
+  </si>
+  <si>
+    <t>Plan de evaluacion</t>
+  </si>
+  <si>
+    <t>* Revisar estructura del proyecto (backend/frontend)
+Analizar * dependencias entre módulos
+* Usar herramientas como análisis estático de código</t>
+  </si>
+  <si>
+    <t>* Alto: Interfaces simples, bien documentadas
+* Medio: Algunas interfaces complejas
+* Bajo: Interfaces difíciles de entender o usar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+* Cantidad de parámetros por interfaz
+* Claridad en contratos (API REST, servicios)
+* Documentación disponible</t>
+  </si>
+  <si>
+    <t>* Revisar endpoints de API de CVAT
+* Analizar documentación técnica
+* Evaluar consistencia en diseño de interfaces</t>
+  </si>
+  <si>
+    <t>Capacidad del sistema para reutilizar componentes en diferentes partes del sistema o en otros proyectos.</t>
+  </si>
+  <si>
+    <t>* Alto: Componentes reutilizados frecuentemente
+* Medio: Reutilización parcial
+* Bajo: Código duplicado o aislado</t>
+  </si>
+  <si>
+    <t>* Uso de librerías internas
+* Componentes compartidos (UI, servicios)
+* Modularización del código</t>
+  </si>
+  <si>
+    <t>* Identificar componentes repetidos
+* Revisar si existen librerías comunes
+* Analizar frontend (React) y backend</t>
+  </si>
+  <si>
+    <t>* Alto (bueno): &lt; 10% duplicación
+* Medio: 10% – 25%
+* Bajo: &gt; 25%</t>
+  </si>
+  <si>
+    <t>* Bloques de código repetidos
+* Falta de funciones reutilizables
+* Ausencia de abstracciones</t>
+  </si>
+  <si>
+    <t>* Usar herramientas como SonarQube
+* Analizar reportes de duplicación
+* Revisar patrones de diseño aplicados</t>
+  </si>
+  <si>
+    <t>Capacidad del sistema para ser entendido fácilmente, detectar errores y realizar diagnósticos.</t>
+  </si>
+  <si>
+    <t>* Bajo (mejor): 1 – 10
+* Medio: 11 – 20
+* Alto (peor): &gt; 20</t>
+  </si>
+  <si>
+    <t>* Cantidad de estructuras de control
+* Funciones demasiado largas
+* Dificultad de comprensión</t>
+  </si>
+  <si>
+    <t>* Analizar funciones críticas
+* Usar herramientas de análisis estático
+* Revisar código manualmente</t>
+  </si>
+  <si>
+    <t>* Alto: &gt; 20% comentarios útiles
+* Medio: 10% – 20%
+* Bajo: &lt; 10%</t>
+  </si>
+  <si>
+    <t>* Claridad de los comentarios
+* Documentación de funciones
+* Uso de estándares (ej: JSDoc, docstrings)</t>
+  </si>
+  <si>
+    <t>* Revisar archivos clave
+* Validar consistencia en comentarios
+* Comparar comentarios vs lógica implementada</t>
+  </si>
+  <si>
+    <t>La madurez evalúa qué tan estable es el sistema en base a la cantidad de errores presentes y el nivel de pruebas implementadas.</t>
+  </si>
+  <si>
+    <t>Mide la cantidad de errores en relación al tamaño del código. Un valor bajo indica mayor estabilidad.</t>
+  </si>
+  <si>
+    <t>* Alto (bueno): &lt; 1 defecto/KLOC
+* Medio: 1 – 5 defectos/KLOC
+* Bajo: &gt; 5 defectos/KLOC</t>
+  </si>
+  <si>
+    <t>* Número de bugs reportados
+* Historial de incidencias
+* Frecuencia de fallos en producción</t>
+  </si>
+  <si>
+    <t>* Revisar issues en repositorio (ej: GitHub)
+* Analizar reportes de bugs
+* Calcular KLOC del proyecto</t>
+  </si>
+  <si>
+    <t>Evalúa qué porcentaje del código está cubierto por pruebas automatizadas.</t>
+  </si>
+  <si>
+    <t>* Alto: &gt; 80%
+* Medio: 50% – 80%
+* Bajo: &lt; 50%</t>
+  </si>
+  <si>
+    <t>* Existencia de pruebas unitarias
+* Pruebas de integración
+* Automatización de testing</t>
+  </si>
+  <si>
+    <t>* Ejecutar herramientas de coverage
+* Revisar pipelines CI/CD
+* Analizar frameworks de testing usados</t>
+  </si>
+  <si>
+    <t>X = Nº funciones con try-catch / Nº funciones
+críticas
+Funciones con recuperación de fallos</t>
+  </si>
+  <si>
+    <t>Capacidad del sistema para seguir funcionando correctamente incluso cuando ocurren errores o fallos internos.</t>
+  </si>
+  <si>
+    <t>Mide qué tan bien el sistema gestiona errores mediante estructuras de control (try-catch) y recuperación.</t>
+  </si>
+  <si>
+    <t>* Uso consistente de try-catch
+* Manejo de errores controlados
+* Evitar fallos no capturados</t>
+  </si>
+  <si>
+    <t>* Revisar funciones críticas del sistema
+* Analizar logs de errores
+* Evaluar comportamiento ante fallos simulados</t>
+  </si>
+  <si>
+    <t>* Alto: 0.80 – 1.00
+* Medio: 0.50 – 0.79
+* Bajo: &lt; 0.50</t>
+  </si>
+  <si>
+    <t>Mide la capacidad del sistema para recuperarse automáticamente ante fallos.</t>
+  </si>
+  <si>
+    <t>* Alto: 0.75 – 1.00
+* Medio: 0.40 – 0.74
+* Bajo: &lt; 0.40</t>
+  </si>
+  <si>
+    <t>* Implementación de reintentos
+* Uso de fallback
+* Manejo de caídas de servicios</t>
+  </si>
+  <si>
+    <t>* Simular fallos (testing)
+* Revisar lógica de reintentos
+* Analizar resiliencia del sistema</t>
+  </si>
+  <si>
+    <t>Evalúa si las operaciones en base de datos cumplen con propiedades ACID (Atomicidad, Consistencia, Aislamiento, Durabilidad).</t>
+  </si>
+  <si>
+    <t>* Alto: 0.90 – 1.00
+* Medio: 0.70 – 0.89
+* Bajo: &lt; 0.70</t>
+  </si>
+  <si>
+    <t>* Uso de transacciones
+* Integridad de datos
+* Manejo de rollback</t>
+  </si>
+  <si>
+    <t>* Revisar ORM o queries
+* Analizar transacciones
+* Probar fallos en BD</t>
+  </si>
+  <si>
+    <t>Mide qué tan bien el sistema registra eventos importantes para monitoreo y diagnóstico.</t>
+  </si>
+  <si>
+    <t>Capacidad del sistema para restaurar su estado y datos después de un fallo.</t>
+  </si>
+  <si>
+    <t>* Registro de errores y eventos
+* Niveles de logging (info, warn, error)
+* Integración con herramientas de monitoreo</t>
+  </si>
+  <si>
+    <t>* Revisar logs del sistema
+* Validar eventos críticos registrados
+* Analizar herramientas usadas (ej: ELK, Grafana)</t>
+  </si>
+  <si>
+    <t>La corrección mide qué tan correctamente el sistema ejecuta sus funciones según los requisitos definidos.</t>
+  </si>
+  <si>
+    <t>Evalúa el porcentaje de casos de uso que se ejecutan correctamente sin errores.</t>
+  </si>
+  <si>
+    <t>* Ejecución correcta de funcionalidades principales
+* Resultados esperados vs obtenidos
+* Errores funcionales detectados</t>
+  </si>
+  <si>
+    <t>* Definir casos de uso clave en CVAT (anotación, exportación,  login, etc.)
+* Ejecutar pruebas funcionales
+* Registrar resultados exitosos/fallidos</t>
+  </si>
+  <si>
+    <t>Mide qué tan bien el sistema valida los datos ingresados por el usuario.</t>
+  </si>
+  <si>
+    <t>* Alto: 0.85 – 1.00
+* Medio: 0.60 – 0.84
+* Bajo: &lt; 0.60</t>
+  </si>
+  <si>
+    <t>* Validación de formularios
+* Manejo de datos inválidos
+* Mensajes de error adecuados</t>
+  </si>
+  <si>
+    <t>* Probar inputs inválidos (formatos incorrectos, vacíos, etc.)
+* Revisar validaciones en frontend y backend
+* Verificar respuestas del sistema</t>
+  </si>
+  <si>
+    <t>La integridad se refiere a la protección del sistema frente a accesos no autorizados y a la correcta gestión de operaciones críticas.</t>
+  </si>
+  <si>
+    <t>Evalúa si el sistema permite el acceso solo a usuarios autorizados.</t>
+  </si>
+  <si>
+    <t>* Alto: 0.95 – 1.00
+* Medio: 0.80 – 0.94
+* Bajo: &lt; 0.80</t>
+  </si>
+  <si>
+    <t>* Implementación de roles y permisos
+* Protección de endpoints
+* Seguridad en autenticación</t>
+  </si>
+  <si>
+    <t>* Intentar accesos con distintos roles
+* Probar endpoints protegidos
+* Validar restricciones de acceso</t>
+  </si>
+  <si>
+    <t>Mide qué porcentaje de operaciones críticas quedan registradas para seguimiento.</t>
+  </si>
+  <si>
+    <t>Alto: 0.85 – 1.00
+Medio: 0.60 – 0.84
+Bajo: &lt; 0.60</t>
+  </si>
+  <si>
+    <t>* Registro de acciones importantes
+* Trazabilidad de cambios
+* Disponibilidad de logs</t>
+  </si>
+  <si>
+    <t>* Identificar operaciones críticas (creación, eliminación, cambios)
+* Revisar logs del sistema
+* Validar si cada operación queda registrada</t>
+  </si>
+  <si>
+    <t>La completitud evalúa si el sistema implementa todas las funcionalidades requeridas.</t>
+  </si>
+  <si>
+    <t>Mide qué tan completo es el soporte de formatos requeridos (ej: imágenes, anotaciones en CVAT).</t>
+  </si>
+  <si>
+    <t>* Compatibilidad con formatos estándar
+* Soporte de exportación/importación
+* Requerimientos del proyecto</t>
+  </si>
+  <si>
+    <t>* Listar formatos requeridos
+* Probar importación/exportación en CVAT
+* Verificar compatibilidad</t>
+  </si>
+  <si>
+    <t>Evalúa si el sistema maneja correctamente situaciones extremas o poco comunes.</t>
+  </si>
+  <si>
+    <t>* Manejo de errores extremos
+* Datos atípicos o grandes volúmenes
+* Respuestas ante fallos inesperados</t>
+  </si>
+  <si>
+    <t>* Identificar casos límite (archivos grandes, datos corruptos, etc.)
+* Ejecutar pruebas de estrés
+* Evaluar comportamiento del sistema</t>
+  </si>
+  <si>
+    <t>Mide la rapidez con la que el sistema responde a las acciones del usuario o solicitudes del sistema.</t>
+  </si>
+  <si>
+    <t>Evalúa el tiempo promedio que tarda la interfaz en responder a una acción del usuario.</t>
+  </si>
+  <si>
+    <t>* Alto (óptimo): 0 – 200 ms
+* Medio: 201 – 500 ms
+* Bajo (deficiente): &gt; 500 ms</t>
+  </si>
+  <si>
+    <t>* Fluidez de la interfaz
+* Tiempo de carga de vistas
+* Respuesta a interacciones (clicks, drag, etc.)</t>
+  </si>
+  <si>
+    <t>* Medir tiempos con herramientas del navegador (DevTools)
+* Ejecutar acciones comunes en CVAT
+* Promediar resultados</t>
+  </si>
+  <si>
+    <t>Mide el porcentaje de llamadas a la API que cumplen con el tiempo máximo definido (SLA).</t>
+  </si>
+  <si>
+    <t>* Tiempo de respuesta de endpoints
+* Cumplimiento de SLA (ej: &lt; 300 ms)
+* Estabilidad de la API</t>
+  </si>
+  <si>
+    <t>* Usar herramientas como Postman o JMeter
+* Ejecutar múltiples requests
+* Medir tiempos y calcular porcentaje</t>
+  </si>
+  <si>
+    <t>Evalúa la habilidad del sistema para manejar cargas de trabajo sin degradar su rendimiento.</t>
+  </si>
+  <si>
+    <t>Mide el número máximo de usuarios simultáneos que el sistema puede soportar manteniendo el SLA.</t>
+  </si>
+  <si>
+    <t>* Alto: &gt; 100 usuarios
+* Medio: 30 – 100 usuarios
+* Bajo: &lt; 30 usuarios</t>
+  </si>
+  <si>
+    <t>* Estabilidad bajo carga
+* Tiempo de respuesta con múltiples usuarios
+* Caídas del sistema</t>
+  </si>
+  <si>
+    <t>* Simular usuarios con herramientas (JMeter, k6)
+* Incrementar carga progresivamente
+* Identificar punto de degradación</t>
+  </si>
+  <si>
+    <t>Evalúa la cantidad de transacciones que el sistema puede procesar por segundo.</t>
+  </si>
+  <si>
+    <t>* Alto: &gt; 100 transacciones/seg
+* Medio: 30 – 100 transacciones/seg
+* Bajo: &lt; 30 transacciones/seg</t>
+  </si>
+  <si>
+    <t>* Capacidad de procesamiento
+* Estabilidad bajo carga
+* Consistencia en resultados</t>
+  </si>
+  <si>
+    <t>Evalúa el consumo de recursos del sistema durante su operación normal.</t>
+  </si>
+  <si>
+    <t>Mide la cantidad promedio de memoria RAM utilizada por el sistema.</t>
+  </si>
+  <si>
+    <t>* Alto (eficiente): &lt; 500 MB
+* Medio: 500 MB – 1.5 GB
+* Bajo (ineficiente): &gt; 1.5 GB</t>
+  </si>
+  <si>
+    <t>* Consumo estable
+* Ausencia de memory leaks
+* Uso eficiente de recursos</t>
+  </si>
+  <si>
+    <t>* Monitorear con herramientas (Docker stats, htop)
+* Ejecutar tareas normales
+* Promediar consumo</t>
+  </si>
+  <si>
+    <t>* Ejecutar pruebas de carga
+* Medir transacciones por segundo
+* Analizar comportamiento del sistema</t>
+  </si>
+  <si>
+    <t>Evalúa el porcentaje promedio de uso del procesador durante la operación.</t>
+  </si>
+  <si>
+    <t>* Alto (eficiente): 0% – 40%
+* Medio: 41% – 70%
+* Bajo (ineficiente): &gt; 70%</t>
+  </si>
+  <si>
+    <t>* Consumo sostenido
+* Picos de CPU
+* Eficiencia de procesamiento</t>
+  </si>
+  <si>
+    <t>* Monitorear CPU durante uso normal
+* Ejecutar operaciones típicas
+* Registrar promedio</t>
+  </si>
+  <si>
+    <t>Mide el porcentaje de tareas que se completan correctamente respecto al total de tareas definidas.</t>
+  </si>
+  <si>
+    <t>* Finalización exitosa de tareas
+* Ausencia de errores durante la ejecución
+* Flujo completo sin bloqueos</t>
+  </si>
+  <si>
+    <t>* Definir tareas clave (ej: crear proyecto, etiquetar imágenes, exportar datos)
+* Observar ejecución por usuarios
+* Registrar tareas completadas vs fallidas</t>
   </si>
 </sst>
 </file>
@@ -547,12 +1013,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -599,6 +1059,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -636,95 +1102,118 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -734,8 +1223,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF9797"/>
       <color rgb="FFAB240D"/>
-      <color rgb="FFFF9797"/>
     </mruColors>
   </colors>
   <extLst>
@@ -750,7 +1239,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1066,628 +1555,1226 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20C261A2-5CD8-43CE-9FA5-A0D2010C6085}">
-  <dimension ref="A1:C77"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H77"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.85546875" customWidth="1"/>
+    <col min="3" max="3" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.42578125" customWidth="1"/>
+    <col min="5" max="5" width="53.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.28515625" customWidth="1"/>
+    <col min="8" max="8" width="27.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-    </row>
-    <row r="2" spans="1:3" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+    </row>
+    <row r="2" spans="1:8" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="C2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="E2" s="21" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="28.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="F2" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="G2" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="H2" s="21" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="106.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="29" t="s">
+        <v>118</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="3" t="s">
+      <c r="F3" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="91.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="29"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="F4" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="91.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="29" t="s">
+        <v>135</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="3" t="s">
+      <c r="F5" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="166.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="29"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="28.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="F6" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="271.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="3" t="s">
+      <c r="F7" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="256.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="29"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+      <c r="F8" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-    </row>
-    <row r="11" spans="1:3" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="24" t="s">
+      <c r="B10" s="32"/>
+      <c r="C10" s="32"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="32"/>
+    </row>
+    <row r="11" spans="1:8" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="C11" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="24" t="s">
+      <c r="D11" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="E11" s="22" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="28.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="20" t="s">
+      <c r="F11" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="G11" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="H11" s="22" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="105.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="30" t="s">
+        <v>149</v>
+      </c>
+      <c r="C12" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="D12" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="E12" s="10" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="20"/>
-      <c r="B13" s="21" t="s">
+      <c r="F12" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="126.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="28"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="D13" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="E13" s="10" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" ht="43.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="20" t="s">
+      <c r="F13" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="113.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="30" t="s">
+        <v>159</v>
+      </c>
+      <c r="C14" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="D14" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="118.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="28"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="E15" s="10" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="20"/>
-      <c r="B15" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="23" t="s">
+      <c r="F15" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="159.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="30" t="s">
+        <v>173</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="E16" s="10" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" s="23" t="s">
+      <c r="F16" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="120" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="28"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="E17" s="10" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="20"/>
-      <c r="B17" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" s="23" t="s">
+      <c r="F17" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+    </row>
+    <row r="19" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="32" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
+      <c r="B19" s="32"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+    </row>
+    <row r="20" spans="1:8" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B20" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="D20" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="E20" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="F20" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="G20" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="H20" s="23" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="106.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-    </row>
-    <row r="20" spans="1:3" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="13" t="s">
+      <c r="B21" s="35" t="s">
+        <v>176</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="106.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="34"/>
+      <c r="B22" s="35"/>
+      <c r="C22" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="91.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="35" t="s">
+        <v>184</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="47.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="34"/>
+      <c r="B24" s="35"/>
+      <c r="C24" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="35" t="s">
+        <v>193</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="91.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="34"/>
+      <c r="B26" s="35"/>
+      <c r="C26" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="E26" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+    </row>
+    <row r="28" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+    </row>
+    <row r="29" spans="1:8" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B29" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="C29" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="D29" s="25"/>
+      <c r="E29" s="25" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="10"/>
-      <c r="B22" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="10"/>
-      <c r="B24" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="10"/>
-      <c r="B26" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="5" t="s">
+      <c r="F29" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="G29" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="H29" s="25" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="91.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-    </row>
-    <row r="29" spans="1:3" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="9" t="s">
+      <c r="B30" s="36" t="s">
+        <v>200</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="33"/>
+      <c r="B31" s="36"/>
+      <c r="C31" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="91.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" s="36" t="s">
+        <v>208</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="33"/>
+      <c r="B33" s="36"/>
+      <c r="C33" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="B34" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="E34" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="33"/>
+      <c r="B35" s="36"/>
+      <c r="C35" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="8"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+    </row>
+    <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="8"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="D37" s="32"/>
+      <c r="E37" s="32"/>
+    </row>
+    <row r="38" spans="1:8" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="8"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B29" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C29" s="9" t="s">
+      <c r="D38" s="14"/>
+      <c r="E38" s="14" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" ht="28.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="B30" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="C30" s="17" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="18"/>
-      <c r="B31" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="C31" s="17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="B32" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="C32" s="17" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="18"/>
-      <c r="B33" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C33" s="19" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="B34" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="C34" s="17" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="18"/>
-      <c r="B35" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="C35" s="17" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="5" t="s">
+      <c r="F38" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="G38" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="H38" s="25" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="28.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="8"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="C37" s="5"/>
-    </row>
-    <row r="38" spans="1:3" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="6" t="s">
+      <c r="D39" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="E39" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="F39" s="37" t="s">
+        <v>169</v>
+      </c>
+      <c r="G39" s="37" t="s">
+        <v>227</v>
+      </c>
+      <c r="H39" s="37" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="8"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="D40" s="26"/>
+      <c r="E40" s="27" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="8"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="D41" s="26"/>
+      <c r="E41" s="27" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="8"/>
+      <c r="B42" s="8"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
+    </row>
+    <row r="43" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="8"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="32" t="s">
+        <v>73</v>
+      </c>
+      <c r="D43" s="32"/>
+      <c r="E43" s="32"/>
+    </row>
+    <row r="44" spans="1:8" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="8"/>
+      <c r="B44" s="8"/>
+      <c r="C44" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="D44" s="15"/>
+      <c r="E44" s="15" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="28.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="C39" s="27" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="C40" s="27" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C41" s="27" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="5" t="s">
+    <row r="45" spans="1:8" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="8"/>
+      <c r="B45" s="8"/>
+      <c r="C45" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="C43" s="5"/>
-    </row>
-    <row r="44" spans="1:3" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="31" t="s">
+      <c r="D45" s="16"/>
+      <c r="E45" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="8"/>
+      <c r="B46" s="8"/>
+      <c r="C46" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="D46" s="16"/>
+      <c r="E46" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="8"/>
+      <c r="B47" s="8"/>
+      <c r="C47" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="D47" s="16"/>
+      <c r="E47" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="8"/>
+      <c r="B48" s="8"/>
+      <c r="C48" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D48" s="16"/>
+      <c r="E48" s="17" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="8"/>
+      <c r="B49" s="8"/>
+      <c r="C49" s="8"/>
+      <c r="D49" s="8"/>
+      <c r="E49" s="8"/>
+    </row>
+    <row r="50" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="8"/>
+      <c r="B50" s="8"/>
+      <c r="C50" s="32" t="s">
+        <v>82</v>
+      </c>
+      <c r="D50" s="32"/>
+      <c r="E50" s="32"/>
+    </row>
+    <row r="51" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="8"/>
+      <c r="B51" s="8"/>
+      <c r="C51" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C44" s="31" t="s">
+      <c r="D51" s="18"/>
+      <c r="E51" s="18" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="C45" s="29" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="30" t="s">
-        <v>76</v>
-      </c>
-      <c r="C46" s="29" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B47" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="C47" s="29" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="C48" s="29" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="49" spans="2:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="5" t="s">
+    <row r="52" spans="1:5" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="8"/>
+      <c r="B52" s="8"/>
+      <c r="C52" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="C50" s="5"/>
-    </row>
-    <row r="51" spans="2:3" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="33" t="s">
+      <c r="D52" s="19"/>
+      <c r="E52" s="20" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="8"/>
+      <c r="B53" s="8"/>
+      <c r="C53" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="D53" s="19"/>
+      <c r="E53" s="20" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="8"/>
+      <c r="B54" s="8"/>
+      <c r="C54" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="D54" s="19"/>
+      <c r="E54" s="20" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="8"/>
+      <c r="B55" s="8"/>
+      <c r="C55" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="D55" s="19"/>
+      <c r="E55" s="20" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="8"/>
+      <c r="B56" s="8"/>
+      <c r="C56" s="8"/>
+      <c r="D56" s="8"/>
+      <c r="E56" s="8"/>
+    </row>
+    <row r="57" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="8"/>
+      <c r="B57" s="8"/>
+      <c r="C57" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="D57" s="32"/>
+      <c r="E57" s="32"/>
+    </row>
+    <row r="58" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="8"/>
+      <c r="B58" s="8"/>
+      <c r="C58" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C51" s="33" t="s">
+      <c r="D58" s="9"/>
+      <c r="E58" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="2:3" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="32" t="s">
-        <v>84</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="53" spans="2:3" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="C53" s="8" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="54" spans="2:3" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="32" t="s">
-        <v>86</v>
-      </c>
-      <c r="C54" s="8" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="55" spans="2:3" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="32" t="s">
-        <v>87</v>
-      </c>
-      <c r="C55" s="8" t="s">
+    <row r="59" spans="1:5" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="8"/>
+      <c r="B59" s="8"/>
+      <c r="C59" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="D59" s="10"/>
+      <c r="E59" s="11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="8"/>
+      <c r="B60" s="8"/>
+      <c r="C60" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="D60" s="10"/>
+      <c r="E60" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="8"/>
+      <c r="B61" s="8"/>
+      <c r="C61" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D61" s="10"/>
+      <c r="E61" s="11" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="8"/>
+      <c r="B62" s="8"/>
+      <c r="C62" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="D62" s="10"/>
+      <c r="E62" s="11" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="8"/>
+      <c r="B63" s="8"/>
+      <c r="C63" s="8"/>
+      <c r="D63" s="8"/>
+      <c r="E63" s="8"/>
+    </row>
+    <row r="64" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="8"/>
+      <c r="B64" s="8"/>
+      <c r="C64" s="32" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="56" spans="2:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C57" s="5"/>
-    </row>
-    <row r="58" spans="2:3" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="24" t="s">
+      <c r="D64" s="32"/>
+      <c r="E64" s="32"/>
+    </row>
+    <row r="65" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="8"/>
+      <c r="B65" s="8"/>
+      <c r="C65" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C58" s="24" t="s">
+      <c r="D65" s="5"/>
+      <c r="E65" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="2:3" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="C59" s="22" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="60" spans="2:3" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="C60" s="22" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="61" spans="2:3" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="C61" s="22" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="62" spans="2:3" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="34" t="s">
-        <v>96</v>
-      </c>
-      <c r="C62" s="22" t="s">
+    <row r="66" spans="1:5" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="8"/>
+      <c r="B66" s="8"/>
+      <c r="C66" s="6" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="63" spans="2:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C64" s="5"/>
-    </row>
-    <row r="65" spans="2:3" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="1" t="s">
+      <c r="D66" s="6"/>
+      <c r="E66" s="7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="8"/>
+      <c r="B67" s="8"/>
+      <c r="C67" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D67" s="6"/>
+      <c r="E67" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="8"/>
+      <c r="B68" s="8"/>
+      <c r="C68" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D68" s="6"/>
+      <c r="E68" s="7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="8"/>
+      <c r="B69" s="8"/>
+      <c r="C69" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D69" s="6"/>
+      <c r="E69" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="8"/>
+      <c r="B70" s="8"/>
+      <c r="C70" s="8"/>
+      <c r="D70" s="8"/>
+      <c r="E70" s="8"/>
+    </row>
+    <row r="71" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="8"/>
+      <c r="B71" s="8"/>
+      <c r="C71" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="D71" s="32"/>
+      <c r="E71" s="32"/>
+    </row>
+    <row r="72" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="8"/>
+      <c r="B72" s="8"/>
+      <c r="C72" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="D72" s="9"/>
+      <c r="E72" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="2:3" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B66" s="35" t="s">
-        <v>101</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="67" spans="2:3" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B67" s="36" t="s">
-        <v>102</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="68" spans="2:3" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="35" t="s">
-        <v>103</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="69" spans="2:3" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="35" t="s">
-        <v>104</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="70" spans="2:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-    <row r="71" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="5" t="s">
+    <row r="73" spans="1:5" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="8"/>
+      <c r="B73" s="8"/>
+      <c r="C73" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="C71" s="5"/>
-    </row>
-    <row r="72" spans="2:3" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B72" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="C72" s="24" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="73" spans="2:3" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B73" s="34" t="s">
+      <c r="D73" s="10"/>
+      <c r="E73" s="11" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="8"/>
+      <c r="B74" s="8"/>
+      <c r="C74" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="C73" s="22" t="s">
+      <c r="D74" s="10"/>
+      <c r="E74" s="11" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="74" spans="2:3" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B74" s="21" t="s">
+    <row r="75" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="8"/>
+      <c r="B75" s="8"/>
+      <c r="C75" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="C74" s="22" t="s">
+      <c r="D75" s="10"/>
+      <c r="E75" s="11" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="75" spans="2:3" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B75" s="34" t="s">
+    <row r="76" spans="1:5" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="8"/>
+      <c r="B76" s="8"/>
+      <c r="C76" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="C75" s="22" t="s">
+      <c r="D76" s="10"/>
+      <c r="E76" s="11" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="76" spans="2:3" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B76" s="34" t="s">
-        <v>113</v>
-      </c>
-      <c r="C76" s="22" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="77" spans="2:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A32:A33"/>
+  <mergeCells count="34">
+    <mergeCell ref="C57:E57"/>
+    <mergeCell ref="C64:E64"/>
+    <mergeCell ref="C71:E71"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="C50:E50"/>
     <mergeCell ref="A34:A35"/>
     <mergeCell ref="A14:A15"/>
     <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A19:E19"/>
     <mergeCell ref="A21:A22"/>
     <mergeCell ref="A23:A24"/>
     <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="B12:B13"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A12:A13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/Tareas en grupo/Metricas Cvat.xlsx
+++ b/Tareas en grupo/Metricas Cvat.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ciencias\Calidad de software - BSPOO\Tareas en grupo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ciencias\CalidadSofwtareBSPO\Tareas en grupo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35FE015E-5EF3-4F94-9409-9CBED4E428EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8470932F-9B98-4691-8D3A-9D4B1921CC3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{5CAAA99B-0B29-425F-89B8-4D79C8DE75EE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5CAAA99B-0B29-425F-89B8-4D79C8DE75EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="303">
   <si>
     <t>Subcaracteristica</t>
   </si>
@@ -944,6 +944,330 @@
     <t>* Definir tareas clave (ej: crear proyecto, etiquetar imágenes, exportar datos)
 * Observar ejecución por usuarios
 * Registrar tareas completadas vs fallidas</t>
+  </si>
+  <si>
+    <t>Mide el porcentaje de resultados correctos generados por el sistema.</t>
+  </si>
+  <si>
+    <t>* Alto: 0.90 – 1.00
+* Medio: 0.75 – 0.89
+* Bajo: &lt; 0.75</t>
+  </si>
+  <si>
+    <t>* Exactitud de anotaciones
+* Consistencia de resultados
+* Comparación con resultados esperados</t>
+  </si>
+  <si>
+    <t>* Comparar resultados con un “ground truth”
+* Evaluar muestras de datos anotados
+* Medir porcentaje de coincidencia</t>
+  </si>
+  <si>
+    <t>Mide el grado en que el sistema permite cumplir los objetivos planteados por el usuario o el proyecto.</t>
+  </si>
+  <si>
+    <t>* Cumplimiento de metas del usuario
+* Soporte del sistema a los objetivos
+* Resultados obtenidos vs esperados</t>
+  </si>
+  <si>
+    <t>* Definir objetivos del uso de CVAT (ej: dataset completo, calidad de anotación)
+* Medir cumplimiento
+* Analizar brechas</t>
+  </si>
+  <si>
+    <t>Compara el número promedio de clics necesarios frente a un escenario óptimo.</t>
+  </si>
+  <si>
+    <t>* Alto (óptimo): 1.00 – 1.20
+* Medio: 1.21 – 1.50
+* Bajo: &gt; 1.50</t>
+  </si>
+  <si>
+    <t>* Número de pasos por tarea
+* Flujo de navegación
+* Existencia de acciones redundantes</t>
+  </si>
+  <si>
+    <t>* Definir tareas clave (ej: crear anotación, exportar dataset)
+* Contar clics reales vs óptimos
+* Calcular promedio</t>
+  </si>
+  <si>
+    <t>Mide qué tan bien el sistema ofrece atajos (teclado o UI) para acelerar tareas frecuentes.</t>
+  </si>
+  <si>
+    <t>* Disponibilidad de shortcuts
+* Facilidad de acceso a atajos
+* Documentación de atajos</t>
+  </si>
+  <si>
+    <t>* Identificar operaciones frecuentes
+* Revisar shortcuts disponibles en CVAT
+* Calcular cobertura</t>
+  </si>
+  <si>
+    <t>Evalúa la cantidad de trabajo que un usuario puede completar en un tiempo determinado.</t>
+  </si>
+  <si>
+    <t>* Alto: &gt; 0.50 tareas/min
+* Medio: 0.20 – 0.50 tareas/min
+* Bajo: &lt; 0.20 tareas/min</t>
+  </si>
+  <si>
+    <t>* Velocidad de ejecución
+* Curva de aprendizaje
+* Fluidez del sistema</t>
+  </si>
+  <si>
+    <t>* Medir tiempo en tareas reales
+* Registrar tareas completadas
+* Calcular productividad promedio</t>
+  </si>
+  <si>
+    <t>Mide el porcentaje de tipos de tarea que cuentan con plantillas reutilizables.</t>
+  </si>
+  <si>
+    <t>* Existencia de configuraciones predefinidas
+* Reutilización de configuraciones
+* Facilidad de uso</t>
+  </si>
+  <si>
+    <t>* Identificar tipos de tareas en CVAT
+* Revisar disponibilidad de plantillas
+* Evaluar utilidad real</t>
+  </si>
+  <si>
+    <t>Mide el promedio de calificaciones otorgadas por los usuarios en una escala definida (ej: 1 a 5).</t>
+  </si>
+  <si>
+    <t>* Alto: 4.0 – 5.0
+* Medio: 3.0 – 3.9
+* Bajo: &lt; 3.0</t>
+  </si>
+  <si>
+    <t>* Aplicar encuestas a usuarios de CVAT
+* Recopilar calificaciones
+* Calcular promedio</t>
+  </si>
+  <si>
+    <t>* Experiencia general del usuario
+* Facilidad de uso
+* Cumplimiento de expectativas</t>
+  </si>
+  <si>
+    <t>Mide la capacidad del sistema para mantener a los usuarios activos a lo largo del tiempo.</t>
+  </si>
+  <si>
+    <t>* Uso continuo del sistema
+* Abandono de usuarios
+* Frecuencia de uso</t>
+  </si>
+  <si>
+    <t>* Analizar métricas de uso mensual
+* Comparar usuarios activos entre periodos
+* Calcular tasa de retención</t>
+  </si>
+  <si>
+    <t>Evalúa la efectividad del soporte técnico en la resolución de problemas de los usuarios.</t>
+  </si>
+  <si>
+    <t>* Resolución efectiva de incidencias
+* Satisfacción con el soporte
+* Seguimiento de casos</t>
+  </si>
+  <si>
+    <t>* Revisar tickets de soporte
+* Evaluar encuestas post-soporte
+* Medir tasa de resolución</t>
+  </si>
+  <si>
+    <t>Mide el tiempo promedio que tarda el sistema de soporte en resolver incidencias.</t>
+  </si>
+  <si>
+    <t>* Alto (óptimo): 0 – 24 horas
+* Medio: 24 – 72 horas
+* Bajo: &gt; 72 horas</t>
+  </si>
+  <si>
+    <t>* Tiempo de respuesta inicial
+* Tiempo total de resolución
+* Complejidad de incidencias</t>
+  </si>
+  <si>
+    <t>* Analizar historial de tickets
+* Calcular tiempos promedio
+* Comparar con SLA definidos</t>
+  </si>
+  <si>
+    <t>Evalúa la capacidad del sistema para proteger los datos contra accesos no autorizados, filtraciones o brechas de seguridad.</t>
+  </si>
+  <si>
+    <t>* Alto (seguro): 0 – 0.01
+* Medio: 0.011 – 0.05
+* Bajo (riesgoso): &gt; 0.05</t>
+  </si>
+  <si>
+    <t>* Incidentes de seguridad reportados
+* Vulnerabilidades detectadas
+* Protección de datos sensibles</t>
+  </si>
+  <si>
+    <t>* Revisar reportes de seguridad
+* Analizar historial de incidentes
+* Evaluar mecanismos de protección</t>
+  </si>
+  <si>
+    <t>Mide el grado en que el sistema cumple con normativas de protección de datos (como GDPR u otras aplicables).</t>
+  </si>
+  <si>
+    <t>* Políticas de privacidad
+* Gestión de datos personales
+* Consentimiento y derechos del usuario</t>
+  </si>
+  <si>
+    <t>* Listar requisitos aplicables
+* Verificar cumplimiento en el sistema
+* Documentar evidencia</t>
+  </si>
+  <si>
+    <t>Evalúa el tiempo en que el sistema está operativo y accesible para los usuarios.</t>
+  </si>
+  <si>
+    <t>* Alto: 0.99 – 1.00 (99% – 100%)
+* Medio: 0.95 – 0.98
+* Bajo: &lt; 0.95</t>
+  </si>
+  <si>
+    <t>* Tiempo de actividad (uptime)
+* Frecuencia de caídas
+* Mantenimiento del sistema</t>
+  </si>
+  <si>
+    <t>* Monitorear uptime (ej: logs, herramientas cloud)
+* Registrar caídas del sistema
+* Calcular porcentaje mensual</t>
+  </si>
+  <si>
+    <t>Mide la capacidad del sistema para evitar la pérdida de datos mediante backups y mecanismos de recuperación.</t>
+  </si>
+  <si>
+    <t>* Existencia de backups automáticos
+* Frecuencia de respaldos
+* Capacidad de restauración</t>
+  </si>
+  <si>
+    <t>* Verificar políticas de backup
+* Simular recuperación de datos
+* Validar integridad de respaldos</t>
+  </si>
+  <si>
+    <t>Evalúa el cumplimiento del sistema con las pautas de accesibilidad web WCAG (Web Content Accessibility Guidelines).</t>
+  </si>
+  <si>
+    <t>* Cumplimiento de WCAG 2.1 o superior
+* Accesibilidad para lectores de pantalla
+* Uso correcto de etiquetas semánticas</t>
+  </si>
+  <si>
+    <t>* Usar herramientas como Lighthouse o WAVE
+* Revisar criterios WCAG aplicables
+* Documentar cumplimiento por criterio</t>
+  </si>
+  <si>
+    <t>Evalúa si el sistema puede ser utilizado completamente mediante teclado, sin necesidad de mouse.</t>
+  </si>
+  <si>
+    <t>* Navegación con Tab/Shift+Tab
+* Acceso a todas las funciones
+* Indicadores de foco visibles</t>
+  </si>
+  <si>
+    <t>* Probar navegación sin mouse
+* Identificar funciones inaccesibles
+* Calcular cobertura</t>
+  </si>
+  <si>
+    <t>Mide el porcentaje de elementos que cumplen con el contraste mínimo recomendado (≥ 4.5:1).</t>
+  </si>
+  <si>
+    <t>* Legibilidad de textos
+* Diferenciación de elementos UI
+* Cumplimiento WCAG (AA o AAA)</t>
+  </si>
+  <si>
+    <t>* Usar herramientas de contraste (Lighthouse, Contrast Checker)
+* Analizar componentes UI
+* Registrar cumplimiento</t>
+  </si>
+  <si>
+    <t>Mide el porcentaje de idiomas soportados respecto a los requeridos.</t>
+  </si>
+  <si>
+    <t>* Disponibilidad de múltiples idiomas
+* Calidad de traducciones
+* Adaptación cultural (localización)</t>
+  </si>
+  <si>
+    <t>* Identificar mercados objetivo
+* Revisar idiomas disponibles en CVAT
+* Evaluar consistencia de traducciones</t>
+  </si>
+  <si>
+    <t>CARACTERÍSTICA 5: ACCESIBILIDAD</t>
+  </si>
+  <si>
+    <t>Evalúa la capacidad del sistema para prevenir errores mediante validaciones y restricciones en la entrada de datos.</t>
+  </si>
+  <si>
+    <t>* Validaciones en formularios
+* Prevención de entradas inválidas
+* Uso de restricciones (tipos, formatos, límites)</t>
+  </si>
+  <si>
+    <t>* Identificar campos de entrada en CVAT
+* Revisar validaciones implementadas
+* Probar entradas incorrectas</t>
+  </si>
+  <si>
+    <t>Evalúa el porcentaje de errores que permiten recuperación sin afectar gravemente la tarea.</t>
+  </si>
+  <si>
+    <t>* Posibilidad de deshacer acciones
+* Conservación de datos
+* Reintentos disponibles</t>
+  </si>
+  <si>
+    <t>* Provocar errores comunes
+* Evaluar si el sistema permite recuperación
+* Registrar resultados</t>
+  </si>
+  <si>
+    <t>Mide el porcentaje de mensajes que son claros, útiles y comprensibles.</t>
+  </si>
+  <si>
+    <t>* Claridad del mensaje
+* Indicación de solución
+* Lenguaje comprensible</t>
+  </si>
+  <si>
+    <t>* Revisar mensajes del sistema
+* Evaluar comprensión por usuarios
+* Clasificar mensajes claros vs confusos</t>
+  </si>
+  <si>
+    <t>Mide el grado en que el sistema proporciona ayuda y documentación para apoyar al usuario.</t>
+  </si>
+  <si>
+    <t>* Existencia de documentación
+* Guías o tutoriales
+* Accesibilidad de ayuda dentro del sistema</t>
+  </si>
+  <si>
+    <t>* Identificar módulos principales de CVAT
+* Revisar documentación disponible
+* Evaluar cobertura</t>
   </si>
 </sst>
 </file>
@@ -990,12 +1314,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1065,8 +1383,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1098,122 +1422,168 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color theme="0"/>
+      </left>
+      <right style="thick">
+        <color theme="0"/>
+      </right>
+      <top style="thick">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0"/>
+      </left>
+      <right style="medium">
+        <color theme="0"/>
+      </right>
+      <top style="medium">
+        <color theme="0"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1239,7 +1609,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1556,7 +1926,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20C261A2-5CD8-43CE-9FA5-A0D2010C6085}">
   <dimension ref="A1:H77"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="49.85546875" customWidth="1"/>
@@ -1569,54 +1939,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
     </row>
     <row r="2" spans="1:8" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="11" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="106.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>12</v>
       </c>
       <c r="F3" s="3" t="s">
@@ -1630,15 +2000,15 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="91.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="29"/>
-      <c r="B4" s="29"/>
-      <c r="C4" s="6" t="s">
+      <c r="A4" s="23"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F4" s="3" t="s">
@@ -1652,19 +2022,19 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="91.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>14</v>
       </c>
       <c r="F5" s="3" t="s">
@@ -1678,15 +2048,15 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="166.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="29"/>
-      <c r="B6" s="29"/>
-      <c r="C6" s="6" t="s">
+      <c r="A6" s="23"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F6" s="3" t="s">
@@ -1700,19 +2070,19 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="271.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F7" s="3" t="s">
@@ -1726,15 +2096,15 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="256.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="29"/>
-      <c r="B8" s="29"/>
-      <c r="C8" s="6" t="s">
+      <c r="A8" s="23"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F8" s="3" t="s">
@@ -1748,61 +2118,61 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
     </row>
     <row r="10" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="32" t="s">
+      <c r="A10" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="32"/>
-      <c r="C10" s="32"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="32"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
     </row>
     <row r="11" spans="1:8" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="D11" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="E11" s="22" t="s">
+      <c r="E11" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="F11" s="22" t="s">
+      <c r="F11" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="G11" s="22" t="s">
+      <c r="G11" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="H11" s="22" t="s">
+      <c r="H11" s="12" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="105.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="28" t="s">
+      <c r="A12" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="30" t="s">
+      <c r="B12" s="24" t="s">
         <v>149</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F12" s="2" t="s">
@@ -1816,15 +2186,15 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="126.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="28"/>
-      <c r="B13" s="30"/>
-      <c r="C13" s="10" t="s">
+      <c r="A13" s="18"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="7" t="s">
         <v>30</v>
       </c>
       <c r="F13" s="2" t="s">
@@ -1838,19 +2208,19 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="113.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="28" t="s">
+      <c r="A14" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="30" t="s">
+      <c r="B14" s="24" t="s">
         <v>159</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="7" t="s">
         <v>158</v>
       </c>
       <c r="F14" s="2" t="s">
@@ -1864,15 +2234,15 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="118.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="28"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="10" t="s">
+      <c r="A15" s="18"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="7" t="s">
         <v>31</v>
       </c>
       <c r="F15" s="2" t="s">
@@ -1886,19 +2256,19 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="159.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="30" t="s">
+      <c r="B16" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F16" s="2" t="s">
@@ -1912,15 +2282,15 @@
       </c>
     </row>
     <row r="17" spans="1:8" ht="120" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="28"/>
-      <c r="B17" s="30"/>
-      <c r="C17" s="10" t="s">
+      <c r="A17" s="18"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="E17" s="7" t="s">
         <v>33</v>
       </c>
       <c r="F17" s="2" t="s">
@@ -1934,61 +2304,61 @@
       </c>
     </row>
     <row r="18" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
     </row>
     <row r="19" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="32" t="s">
+      <c r="A19" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="B19" s="32"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
     </row>
     <row r="20" spans="1:8" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="24" t="s">
+      <c r="A20" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B20" s="24" t="s">
+      <c r="B20" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="C20" s="24" t="s">
+      <c r="C20" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="D20" s="24" t="s">
+      <c r="D20" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="E20" s="23" t="s">
+      <c r="E20" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="F20" s="23" t="s">
+      <c r="F20" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="G20" s="23" t="s">
+      <c r="G20" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="H20" s="23" t="s">
+      <c r="H20" s="13" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="106.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="34" t="s">
+      <c r="A21" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="B21" s="35" t="s">
+      <c r="B21" s="20" t="s">
         <v>176</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D21" s="16" t="s">
+      <c r="D21" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="E21" s="16" t="s">
+      <c r="E21" s="10" t="s">
         <v>44</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -2002,15 +2372,15 @@
       </c>
     </row>
     <row r="22" spans="1:8" ht="106.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="34"/>
-      <c r="B22" s="35"/>
-      <c r="C22" s="16" t="s">
+      <c r="A22" s="19"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="E22" s="16" t="s">
+      <c r="E22" s="10" t="s">
         <v>45</v>
       </c>
       <c r="F22" s="1" t="s">
@@ -2024,19 +2394,19 @@
       </c>
     </row>
     <row r="23" spans="1:8" ht="91.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="34" t="s">
+      <c r="A23" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="35" t="s">
+      <c r="B23" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="D23" s="16" t="s">
+      <c r="D23" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="E23" s="16" t="s">
+      <c r="E23" s="10" t="s">
         <v>46</v>
       </c>
       <c r="F23" s="1" t="s">
@@ -2050,15 +2420,15 @@
       </c>
     </row>
     <row r="24" spans="1:8" ht="47.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="34"/>
-      <c r="B24" s="35"/>
-      <c r="C24" s="16" t="s">
+      <c r="A24" s="19"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="D24" s="16" t="s">
+      <c r="D24" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="E24" s="16" t="s">
+      <c r="E24" s="10" t="s">
         <v>47</v>
       </c>
       <c r="F24" s="1" t="s">
@@ -2072,19 +2442,19 @@
       </c>
     </row>
     <row r="25" spans="1:8" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="34" t="s">
+      <c r="A25" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="35" t="s">
+      <c r="B25" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="C25" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D25" s="16" t="s">
+      <c r="D25" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="E25" s="16" t="s">
+      <c r="E25" s="10" t="s">
         <v>48</v>
       </c>
       <c r="F25" s="1" t="s">
@@ -2098,15 +2468,15 @@
       </c>
     </row>
     <row r="26" spans="1:8" ht="91.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="34"/>
-      <c r="B26" s="35"/>
-      <c r="C26" s="16" t="s">
+      <c r="A26" s="19"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D26" s="16" t="s">
+      <c r="D26" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="E26" s="16" t="s">
+      <c r="E26" s="10" t="s">
         <v>49</v>
       </c>
       <c r="F26" s="1" t="s">
@@ -2120,59 +2490,59 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
+      <c r="A27" s="6"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
     </row>
     <row r="28" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="32" t="s">
+      <c r="A28" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="B28" s="32"/>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
     </row>
     <row r="29" spans="1:8" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="12" t="s">
+      <c r="A29" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B29" s="25" t="s">
+      <c r="B29" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="C29" s="25" t="s">
+      <c r="C29" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D29" s="25"/>
-      <c r="E29" s="25" t="s">
+      <c r="D29" s="15"/>
+      <c r="E29" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="F29" s="25" t="s">
+      <c r="F29" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="G29" s="25" t="s">
+      <c r="G29" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="H29" s="25" t="s">
+      <c r="H29" s="15" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="91.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="33" t="s">
+      <c r="A30" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="B30" s="36" t="s">
+      <c r="B30" s="21" t="s">
         <v>200</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="D30" s="13" t="s">
+      <c r="D30" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="E30" s="13" t="s">
+      <c r="E30" s="9" t="s">
         <v>60</v>
       </c>
       <c r="F30" s="4" t="s">
@@ -2186,15 +2556,15 @@
       </c>
     </row>
     <row r="31" spans="1:8" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="33"/>
-      <c r="B31" s="36"/>
-      <c r="C31" s="13" t="s">
+      <c r="A31" s="17"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="D31" s="13" t="s">
+      <c r="D31" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="E31" s="13" t="s">
+      <c r="E31" s="9" t="s">
         <v>61</v>
       </c>
       <c r="F31" s="4" t="s">
@@ -2208,19 +2578,19 @@
       </c>
     </row>
     <row r="32" spans="1:8" ht="91.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="33" t="s">
+      <c r="A32" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="B32" s="36" t="s">
+      <c r="B32" s="21" t="s">
         <v>208</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="C32" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="D32" s="13" t="s">
+      <c r="D32" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="E32" s="13" t="s">
+      <c r="E32" s="9" t="s">
         <v>62</v>
       </c>
       <c r="F32" s="4" t="s">
@@ -2234,15 +2604,15 @@
       </c>
     </row>
     <row r="33" spans="1:8" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="33"/>
-      <c r="B33" s="36"/>
-      <c r="C33" s="13" t="s">
+      <c r="A33" s="17"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="D33" s="13" t="s">
+      <c r="D33" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="E33" s="13" t="s">
+      <c r="E33" s="9" t="s">
         <v>63</v>
       </c>
       <c r="F33" s="4" t="s">
@@ -2256,19 +2626,19 @@
       </c>
     </row>
     <row r="34" spans="1:8" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="33" t="s">
+      <c r="A34" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="B34" s="36" t="s">
+      <c r="B34" s="21" t="s">
         <v>216</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="C34" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="D34" s="13" t="s">
+      <c r="D34" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="E34" s="13" t="s">
+      <c r="E34" s="9" t="s">
         <v>64</v>
       </c>
       <c r="F34" s="4" t="s">
@@ -2282,15 +2652,15 @@
       </c>
     </row>
     <row r="35" spans="1:8" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="33"/>
-      <c r="B35" s="36"/>
-      <c r="C35" s="13" t="s">
+      <c r="A35" s="17"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="D35" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="E35" s="13" t="s">
+      <c r="E35" s="9" t="s">
         <v>65</v>
       </c>
       <c r="F35" s="4" t="s">
@@ -2304,29 +2674,31 @@
       </c>
     </row>
     <row r="36" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="8"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
+      <c r="A36" s="6"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
     </row>
     <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="8"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="32" t="s">
+      <c r="A37" s="6"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="D37" s="32"/>
-      <c r="E37" s="32"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
     </row>
     <row r="38" spans="1:8" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="8"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="14" t="s">
+      <c r="A38" s="6"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14" t="s">
+      <c r="D38" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="E38" s="25" t="s">
         <v>2</v>
       </c>
       <c r="F38" s="25" t="s">
@@ -2339,427 +2711,693 @@
         <v>130</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="28.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="8"/>
-      <c r="B39" s="8"/>
+    <row r="39" spans="1:8" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="6"/>
+      <c r="B39" s="6"/>
       <c r="C39" s="26" t="s">
         <v>67</v>
       </c>
       <c r="D39" s="26" t="s">
         <v>226</v>
       </c>
-      <c r="E39" s="27" t="s">
+      <c r="E39" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="F39" s="37" t="s">
+      <c r="F39" s="27" t="s">
         <v>169</v>
       </c>
-      <c r="G39" s="37" t="s">
+      <c r="G39" s="27" t="s">
         <v>227</v>
       </c>
-      <c r="H39" s="37" t="s">
+      <c r="H39" s="27" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="8"/>
-      <c r="B40" s="8"/>
+    <row r="40" spans="1:8" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="6"/>
+      <c r="B40" s="6"/>
       <c r="C40" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="D40" s="26"/>
-      <c r="E40" s="27" t="s">
+      <c r="D40" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="E40" s="26" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="8"/>
-      <c r="B41" s="8"/>
+      <c r="F40" s="27" t="s">
+        <v>230</v>
+      </c>
+      <c r="G40" s="27" t="s">
+        <v>231</v>
+      </c>
+      <c r="H40" s="27" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="6"/>
+      <c r="B41" s="6"/>
       <c r="C41" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="D41" s="26"/>
-      <c r="E41" s="27" t="s">
+      <c r="D41" s="26" t="s">
+        <v>233</v>
+      </c>
+      <c r="E41" s="26" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="8"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
+      <c r="F41" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="G41" s="27" t="s">
+        <v>234</v>
+      </c>
+      <c r="H41" s="27" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="6"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
     </row>
     <row r="43" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="8"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="32" t="s">
+      <c r="A43" s="6"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="D43" s="32"/>
-      <c r="E43" s="32"/>
-    </row>
-    <row r="44" spans="1:8" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="8"/>
-      <c r="B44" s="8"/>
-      <c r="C44" s="15" t="s">
+      <c r="D43" s="28"/>
+      <c r="E43" s="28"/>
+    </row>
+    <row r="44" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="6"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="D44" s="15"/>
-      <c r="E44" s="15" t="s">
+      <c r="D44" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="E44" s="29" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="8"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="16" t="s">
+      <c r="F44" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="G44" s="29" t="s">
+        <v>127</v>
+      </c>
+      <c r="H44" s="29" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="6"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="D45" s="16"/>
-      <c r="E45" s="17" t="s">
+      <c r="D45" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="E45" s="30" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="8"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="16" t="s">
+      <c r="F45" s="31" t="s">
+        <v>237</v>
+      </c>
+      <c r="G45" s="31" t="s">
+        <v>238</v>
+      </c>
+      <c r="H45" s="31" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="6"/>
+      <c r="B46" s="6"/>
+      <c r="C46" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="D46" s="16"/>
-      <c r="E46" s="17" t="s">
+      <c r="D46" s="30" t="s">
+        <v>240</v>
+      </c>
+      <c r="E46" s="30" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="8"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="16" t="s">
+      <c r="F46" s="31" t="s">
+        <v>163</v>
+      </c>
+      <c r="G46" s="31" t="s">
+        <v>241</v>
+      </c>
+      <c r="H46" s="31" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="6"/>
+      <c r="B47" s="6"/>
+      <c r="C47" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="D47" s="16"/>
-      <c r="E47" s="17" t="s">
+      <c r="D47" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="E47" s="30" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="8"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="16" t="s">
+      <c r="F47" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="G47" s="31" t="s">
+        <v>245</v>
+      </c>
+      <c r="H47" s="31" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="6"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="D48" s="16"/>
-      <c r="E48" s="17" t="s">
+      <c r="D48" s="30" t="s">
+        <v>247</v>
+      </c>
+      <c r="E48" s="30" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="8"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-    </row>
-    <row r="50" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="8"/>
-      <c r="B50" s="8"/>
-      <c r="C50" s="32" t="s">
+      <c r="F48" s="31" t="s">
+        <v>165</v>
+      </c>
+      <c r="G48" s="31" t="s">
+        <v>248</v>
+      </c>
+      <c r="H48" s="31" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="6"/>
+      <c r="B49" s="6"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+    </row>
+    <row r="50" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="6"/>
+      <c r="B50" s="6"/>
+      <c r="C50" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="D50" s="32"/>
-      <c r="E50" s="32"/>
-    </row>
-    <row r="51" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="8"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="18" t="s">
+      <c r="D50" s="28"/>
+      <c r="E50" s="28"/>
+    </row>
+    <row r="51" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="6"/>
+      <c r="B51" s="6"/>
+      <c r="C51" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="D51" s="18"/>
-      <c r="E51" s="18" t="s">
+      <c r="D51" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="E51" s="32" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="8"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="19" t="s">
+      <c r="F51" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="G51" s="32" t="s">
+        <v>127</v>
+      </c>
+      <c r="H51" s="32" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="6"/>
+      <c r="B52" s="6"/>
+      <c r="C52" s="33" t="s">
         <v>83</v>
       </c>
-      <c r="D52" s="19"/>
-      <c r="E52" s="20" t="s">
+      <c r="D52" s="33" t="s">
+        <v>250</v>
+      </c>
+      <c r="E52" s="33" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="8"/>
-      <c r="B53" s="8"/>
-      <c r="C53" s="19" t="s">
+      <c r="F52" s="34" t="s">
+        <v>251</v>
+      </c>
+      <c r="G52" s="34" t="s">
+        <v>253</v>
+      </c>
+      <c r="H52" s="34" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="6"/>
+      <c r="B53" s="6"/>
+      <c r="C53" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="D53" s="19"/>
-      <c r="E53" s="20" t="s">
+      <c r="D53" s="33" t="s">
+        <v>254</v>
+      </c>
+      <c r="E53" s="33" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="8"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="19" t="s">
+      <c r="F53" s="34" t="s">
+        <v>163</v>
+      </c>
+      <c r="G53" s="34" t="s">
+        <v>255</v>
+      </c>
+      <c r="H53" s="34" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="6"/>
+      <c r="B54" s="6"/>
+      <c r="C54" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="D54" s="19"/>
-      <c r="E54" s="20" t="s">
+      <c r="D54" s="33" t="s">
+        <v>257</v>
+      </c>
+      <c r="E54" s="33" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="8"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="19" t="s">
+      <c r="F54" s="34" t="s">
+        <v>181</v>
+      </c>
+      <c r="G54" s="34" t="s">
+        <v>258</v>
+      </c>
+      <c r="H54" s="34" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="6"/>
+      <c r="B55" s="6"/>
+      <c r="C55" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="D55" s="19"/>
-      <c r="E55" s="20" t="s">
+      <c r="D55" s="33" t="s">
+        <v>260</v>
+      </c>
+      <c r="E55" s="33" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="8"/>
-      <c r="B56" s="8"/>
-      <c r="C56" s="8"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-    </row>
-    <row r="57" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="8"/>
-      <c r="B57" s="8"/>
-      <c r="C57" s="32" t="s">
+      <c r="F55" s="34" t="s">
+        <v>261</v>
+      </c>
+      <c r="G55" s="34" t="s">
+        <v>262</v>
+      </c>
+      <c r="H55" s="34" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="6"/>
+      <c r="B56" s="6"/>
+      <c r="C56" s="6"/>
+      <c r="D56" s="6"/>
+      <c r="E56" s="6"/>
+    </row>
+    <row r="57" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="6"/>
+      <c r="B57" s="6"/>
+      <c r="C57" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="D57" s="32"/>
-      <c r="E57" s="32"/>
-    </row>
-    <row r="58" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="8"/>
-      <c r="B58" s="8"/>
-      <c r="C58" s="9" t="s">
+      <c r="D57" s="28"/>
+      <c r="E57" s="28"/>
+    </row>
+    <row r="58" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="6"/>
+      <c r="B58" s="6"/>
+      <c r="C58" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="D58" s="9"/>
-      <c r="E58" s="9" t="s">
+      <c r="D58" s="36" t="s">
+        <v>119</v>
+      </c>
+      <c r="E58" s="36" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="8"/>
-      <c r="B59" s="8"/>
-      <c r="C59" s="10" t="s">
+      <c r="F58" s="35" t="s">
+        <v>126</v>
+      </c>
+      <c r="G58" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="H58" s="35" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="6"/>
+      <c r="B59" s="6"/>
+      <c r="C59" s="37" t="s">
         <v>92</v>
       </c>
-      <c r="D59" s="10"/>
-      <c r="E59" s="11" t="s">
+      <c r="D59" s="37" t="s">
+        <v>264</v>
+      </c>
+      <c r="E59" s="38" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="8"/>
-      <c r="B60" s="8"/>
-      <c r="C60" s="10" t="s">
+      <c r="F59" s="39" t="s">
+        <v>265</v>
+      </c>
+      <c r="G59" s="39" t="s">
+        <v>266</v>
+      </c>
+      <c r="H59" s="39" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="6"/>
+      <c r="B60" s="6"/>
+      <c r="C60" s="37" t="s">
         <v>93</v>
       </c>
-      <c r="D60" s="10"/>
-      <c r="E60" s="11" t="s">
+      <c r="D60" s="37" t="s">
+        <v>268</v>
+      </c>
+      <c r="E60" s="38" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="8"/>
-      <c r="B61" s="8"/>
-      <c r="C61" s="10" t="s">
+      <c r="F60" s="39" t="s">
+        <v>169</v>
+      </c>
+      <c r="G60" s="39" t="s">
+        <v>269</v>
+      </c>
+      <c r="H60" s="39" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="6"/>
+      <c r="B61" s="6"/>
+      <c r="C61" s="37" t="s">
         <v>94</v>
       </c>
-      <c r="D61" s="10"/>
-      <c r="E61" s="11" t="s">
+      <c r="D61" s="37" t="s">
+        <v>271</v>
+      </c>
+      <c r="E61" s="38" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="8"/>
-      <c r="B62" s="8"/>
-      <c r="C62" s="10" t="s">
+      <c r="F61" s="39" t="s">
+        <v>272</v>
+      </c>
+      <c r="G61" s="39" t="s">
+        <v>273</v>
+      </c>
+      <c r="H61" s="39" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="6"/>
+      <c r="B62" s="6"/>
+      <c r="C62" s="37" t="s">
         <v>95</v>
       </c>
-      <c r="D62" s="10"/>
-      <c r="E62" s="11" t="s">
+      <c r="D62" s="37" t="s">
+        <v>275</v>
+      </c>
+      <c r="E62" s="38" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="8"/>
-      <c r="B63" s="8"/>
-      <c r="C63" s="8"/>
-      <c r="D63" s="8"/>
-      <c r="E63" s="8"/>
-    </row>
-    <row r="64" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="8"/>
-      <c r="B64" s="8"/>
-      <c r="C64" s="32" t="s">
-        <v>91</v>
-      </c>
-      <c r="D64" s="32"/>
-      <c r="E64" s="32"/>
-    </row>
-    <row r="65" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="8"/>
-      <c r="B65" s="8"/>
-      <c r="C65" s="5" t="s">
+      <c r="F62" s="39" t="s">
+        <v>169</v>
+      </c>
+      <c r="G62" s="39" t="s">
+        <v>276</v>
+      </c>
+      <c r="H62" s="39" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="6"/>
+      <c r="B63" s="6"/>
+      <c r="C63" s="6"/>
+      <c r="D63" s="6"/>
+      <c r="E63" s="6"/>
+    </row>
+    <row r="64" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="6"/>
+      <c r="B64" s="6"/>
+      <c r="C64" s="28" t="s">
+        <v>290</v>
+      </c>
+      <c r="D64" s="28"/>
+      <c r="E64" s="28"/>
+    </row>
+    <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="6"/>
+      <c r="B65" s="6"/>
+      <c r="C65" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="D65" s="5"/>
-      <c r="E65" s="5" t="s">
+      <c r="D65" s="40" t="s">
+        <v>119</v>
+      </c>
+      <c r="E65" s="40" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="8"/>
-      <c r="B66" s="8"/>
-      <c r="C66" s="6" t="s">
+      <c r="F65" s="40" t="s">
+        <v>126</v>
+      </c>
+      <c r="G65" s="40" t="s">
+        <v>127</v>
+      </c>
+      <c r="H65" s="40" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="6"/>
+      <c r="B66" s="6"/>
+      <c r="C66" s="41" t="s">
         <v>100</v>
       </c>
-      <c r="D66" s="6"/>
-      <c r="E66" s="7" t="s">
+      <c r="D66" s="41" t="s">
+        <v>278</v>
+      </c>
+      <c r="E66" s="41" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="8"/>
-      <c r="B67" s="8"/>
-      <c r="C67" s="6" t="s">
+      <c r="F66" s="42" t="s">
+        <v>169</v>
+      </c>
+      <c r="G66" s="42" t="s">
+        <v>279</v>
+      </c>
+      <c r="H66" s="42" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="6"/>
+      <c r="B67" s="6"/>
+      <c r="C67" s="41" t="s">
         <v>101</v>
       </c>
-      <c r="D67" s="6"/>
-      <c r="E67" s="7" t="s">
+      <c r="D67" s="41" t="s">
+        <v>281</v>
+      </c>
+      <c r="E67" s="41" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="8"/>
-      <c r="B68" s="8"/>
-      <c r="C68" s="6" t="s">
+      <c r="F67" s="42" t="s">
+        <v>181</v>
+      </c>
+      <c r="G67" s="42" t="s">
+        <v>282</v>
+      </c>
+      <c r="H67" s="42" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="6"/>
+      <c r="B68" s="6"/>
+      <c r="C68" s="41" t="s">
         <v>102</v>
       </c>
-      <c r="D68" s="6"/>
-      <c r="E68" s="7" t="s">
+      <c r="D68" s="41" t="s">
+        <v>284</v>
+      </c>
+      <c r="E68" s="41" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="8"/>
-      <c r="B69" s="8"/>
-      <c r="C69" s="6" t="s">
+      <c r="F68" s="42" t="s">
+        <v>169</v>
+      </c>
+      <c r="G68" s="42" t="s">
+        <v>285</v>
+      </c>
+      <c r="H68" s="42" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="6"/>
+      <c r="B69" s="6"/>
+      <c r="C69" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="D69" s="6"/>
-      <c r="E69" s="7" t="s">
+      <c r="D69" s="41" t="s">
+        <v>287</v>
+      </c>
+      <c r="E69" s="41" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="8"/>
-      <c r="B70" s="8"/>
-      <c r="C70" s="8"/>
-      <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
-    </row>
-    <row r="71" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="8"/>
-      <c r="B71" s="8"/>
-      <c r="C71" s="32" t="s">
+      <c r="F69" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="G69" s="42" t="s">
+        <v>288</v>
+      </c>
+      <c r="H69" s="42" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="6"/>
+      <c r="B70" s="6"/>
+      <c r="C70" s="6"/>
+      <c r="D70" s="6"/>
+      <c r="E70" s="6"/>
+    </row>
+    <row r="72" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C72" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="D71" s="32"/>
-      <c r="E71" s="32"/>
-    </row>
-    <row r="72" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="8"/>
-      <c r="B72" s="8"/>
-      <c r="C72" s="9" t="s">
+      <c r="D72" s="28"/>
+      <c r="E72" s="28"/>
+    </row>
+    <row r="73" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C73" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="D72" s="9"/>
-      <c r="E72" s="9" t="s">
+      <c r="D73" s="35" t="s">
+        <v>119</v>
+      </c>
+      <c r="E73" s="35" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="8"/>
-      <c r="B73" s="8"/>
-      <c r="C73" s="10" t="s">
+      <c r="F73" s="35" t="s">
+        <v>126</v>
+      </c>
+      <c r="G73" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="H73" s="35" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C74" s="37" t="s">
         <v>109</v>
       </c>
-      <c r="D73" s="10"/>
-      <c r="E73" s="11" t="s">
+      <c r="D74" s="37" t="s">
+        <v>291</v>
+      </c>
+      <c r="E74" s="37" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="74" spans="1:5" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="8"/>
-      <c r="B74" s="8"/>
-      <c r="C74" s="10" t="s">
+      <c r="F74" s="43" t="s">
+        <v>169</v>
+      </c>
+      <c r="G74" s="43" t="s">
+        <v>292</v>
+      </c>
+      <c r="H74" s="43" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C75" s="37" t="s">
         <v>110</v>
       </c>
-      <c r="D74" s="10"/>
-      <c r="E74" s="11" t="s">
+      <c r="D75" s="37" t="s">
+        <v>294</v>
+      </c>
+      <c r="E75" s="37" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="75" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="8"/>
-      <c r="B75" s="8"/>
-      <c r="C75" s="10" t="s">
+      <c r="F75" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="G75" s="43" t="s">
+        <v>295</v>
+      </c>
+      <c r="H75" s="43" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C76" s="37" t="s">
         <v>111</v>
       </c>
-      <c r="D75" s="10"/>
-      <c r="E75" s="11" t="s">
+      <c r="D76" s="37" t="s">
+        <v>297</v>
+      </c>
+      <c r="E76" s="37" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="76" spans="1:5" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="8"/>
-      <c r="B76" s="8"/>
-      <c r="C76" s="10" t="s">
+      <c r="F76" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="G76" s="43" t="s">
+        <v>298</v>
+      </c>
+      <c r="H76" s="43" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C77" s="37" t="s">
         <v>112</v>
       </c>
-      <c r="D76" s="10"/>
-      <c r="E76" s="11" t="s">
+      <c r="D77" s="37" t="s">
+        <v>300</v>
+      </c>
+      <c r="E77" s="37" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="77" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+      <c r="F77" s="43" t="s">
+        <v>163</v>
+      </c>
+      <c r="G77" s="43" t="s">
+        <v>301</v>
+      </c>
+      <c r="H77" s="43" t="s">
+        <v>302</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="C57:E57"/>
-    <mergeCell ref="C64:E64"/>
-    <mergeCell ref="C71:E71"/>
-    <mergeCell ref="C43:E43"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C72:E72"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A28:E28"/>
@@ -2775,6 +3413,24 @@
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C57:E57"/>
+    <mergeCell ref="C64:E64"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="C50:E50"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
